--- a/downloads/ErsteBude_Budget_Tabelle.xlsx
+++ b/downloads/ErsteBude_Budget_Tabelle.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Betreibungsauszug und Kopien</t>
   </si>
   <si>
-    <t xml:space="preserve">Gebühr beim Betreibungsamt deiner Gemeinde prüfen.</t>
+    <t xml:space="preserve">Betreibungsamt CHF 17, online bei der Post CHF 26.90.</t>
   </si>
   <si>
     <t xml:space="preserve">Sonstiges / Reserve</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Serafe (Radio- und Fernsehabgabe)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jahresbetrag auf serafe.ch prüfen und durch 12 teilen. In der WG wird sie geteilt.</t>
+    <t xml:space="preserve">Ab 2027 CHF 312 pro Jahr (CHF 26 pro Monat). Eine WG zahlt sie nur einmal und teilt.</t>
   </si>
   <si>
     <t xml:space="preserve">Hausrat- und Privathaftpflichtversicherung</t>
@@ -964,7 +964,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>33</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>36</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">SUM(C21:C30)</f>
-        <v>1988</v>
+        <v>2026</v>
       </c>
       <c r="D31" s="14"/>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C40" s="17" t="n">
         <f aca="false">C37-C31</f>
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>51</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C42" s="20" t="n">
         <f aca="false">IF(C40&gt;0,ROUNDUP(C18/C40,0),"–")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>55</v>
